--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 2 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A464AE3E-03AB-4A40-95ED-A324A231A390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9055E1B6-1567-491A-BD51-4E00B18A9862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="176">
   <si>
     <t>CPF</t>
   </si>
@@ -551,19 +551,13 @@
   </si>
   <si>
     <t>ESCOLA ESTADUAL PROFESSORA DIVA GOMES DA SILVEIRA COSTA</t>
-  </si>
-  <si>
-    <t>FUNDAÇÃO GETULIO VARGAS</t>
-  </si>
-  <si>
-    <t>123.456.789-10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -618,9 +612,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -658,7 +652,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -764,7 +758,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -906,7 +900,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -914,15 +908,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D152"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:D151"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -936,7 +930,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -947,7 +941,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -958,7 +952,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>172</v>
       </c>
@@ -969,7 +963,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -980,7 +974,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -991,7 +985,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1002,7 +996,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1013,7 +1007,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1024,7 +1018,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1035,7 +1029,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1046,7 +1040,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1057,7 +1051,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1068,7 +1062,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1079,7 +1073,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1090,7 +1084,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1101,7 +1095,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -1112,7 +1106,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -1123,7 +1117,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -1134,7 +1128,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -1145,7 +1139,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -1156,7 +1150,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -1167,7 +1161,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -1178,7 +1172,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -1189,7 +1183,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -1200,7 +1194,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -1211,7 +1205,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>51</v>
       </c>
@@ -1222,7 +1216,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -1233,7 +1227,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -1244,7 +1238,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -1255,7 +1249,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -1266,7 +1260,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -1277,7 +1271,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -1288,7 +1282,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>65</v>
       </c>
@@ -1299,7 +1293,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>67</v>
       </c>
@@ -1310,7 +1304,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>69</v>
       </c>
@@ -1321,7 +1315,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>71</v>
       </c>
@@ -1332,7 +1326,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>73</v>
       </c>
@@ -1343,7 +1337,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>75</v>
       </c>
@@ -1354,7 +1348,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>77</v>
       </c>
@@ -1365,7 +1359,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>79</v>
       </c>
@@ -1376,7 +1370,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>81</v>
       </c>
@@ -1387,7 +1381,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>83</v>
       </c>
@@ -1398,7 +1392,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>61</v>
       </c>
@@ -1409,7 +1403,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>85</v>
       </c>
@@ -1420,7 +1414,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>63</v>
       </c>
@@ -1431,7 +1425,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>87</v>
       </c>
@@ -1442,7 +1436,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>89</v>
       </c>
@@ -1453,7 +1447,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>39</v>
       </c>
@@ -1464,7 +1458,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>41</v>
       </c>
@@ -1475,7 +1469,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>65</v>
       </c>
@@ -1486,7 +1480,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>91</v>
       </c>
@@ -1497,7 +1491,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>93</v>
       </c>
@@ -1508,7 +1502,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>95</v>
       </c>
@@ -1519,7 +1513,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>97</v>
       </c>
@@ -1530,7 +1524,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>67</v>
       </c>
@@ -1541,7 +1535,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>51</v>
       </c>
@@ -1552,7 +1546,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>99</v>
       </c>
@@ -1563,7 +1557,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -1574,7 +1568,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>71</v>
       </c>
@@ -1585,7 +1579,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>73</v>
       </c>
@@ -1596,7 +1590,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -1607,7 +1601,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>3</v>
       </c>
@@ -1618,7 +1612,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>53</v>
       </c>
@@ -1629,7 +1623,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -1640,7 +1634,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>27</v>
       </c>
@@ -1651,7 +1645,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>101</v>
       </c>
@@ -1662,7 +1656,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>103</v>
       </c>
@@ -1673,7 +1667,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -1684,7 +1678,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>19</v>
       </c>
@@ -1695,7 +1689,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -1706,7 +1700,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>43</v>
       </c>
@@ -1717,7 +1711,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>13</v>
       </c>
@@ -1728,7 +1722,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>79</v>
       </c>
@@ -1739,7 +1733,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>21</v>
       </c>
@@ -1750,7 +1744,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -1761,7 +1755,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>15</v>
       </c>
@@ -1772,7 +1766,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -1783,7 +1777,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>31</v>
       </c>
@@ -1794,7 +1788,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>45</v>
       </c>
@@ -1805,7 +1799,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>81</v>
       </c>
@@ -1816,7 +1810,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>33</v>
       </c>
@@ -1827,7 +1821,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>55</v>
       </c>
@@ -1838,7 +1832,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>23</v>
       </c>
@@ -1849,7 +1843,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>35</v>
       </c>
@@ -1860,7 +1854,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>35</v>
       </c>
@@ -1871,7 +1865,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>105</v>
       </c>
@@ -1882,7 +1876,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>57</v>
       </c>
@@ -1893,7 +1887,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>107</v>
       </c>
@@ -1904,7 +1898,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>49</v>
       </c>
@@ -1915,7 +1909,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>37</v>
       </c>
@@ -1926,7 +1920,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>109</v>
       </c>
@@ -1937,7 +1931,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>111</v>
       </c>
@@ -1948,7 +1942,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>113</v>
       </c>
@@ -1959,7 +1953,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>59</v>
       </c>
@@ -1970,7 +1964,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>115</v>
       </c>
@@ -1982,7 +1976,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>116</v>
       </c>
@@ -1993,608 +1987,597 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>176</v>
-      </c>
-      <c r="B98" t="s">
-        <v>177</v>
+        <v>118</v>
+      </c>
+      <c r="C98">
+        <v>17021502</v>
       </c>
       <c r="D98">
         <v>123456</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" t="s">
-        <v>118</v>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="C99">
-        <v>17021502</v>
+        <v>17021685</v>
       </c>
       <c r="D99">
         <v>123456</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C100">
-        <v>17021685</v>
+        <v>17021553</v>
       </c>
       <c r="D100">
         <v>123456</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C101">
-        <v>17021553</v>
+        <v>17052351</v>
       </c>
       <c r="D101">
         <v>123456</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C102">
-        <v>17052351</v>
+        <v>17021243</v>
       </c>
       <c r="D102">
         <v>123456</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C103">
-        <v>17021243</v>
+        <v>17023181</v>
       </c>
       <c r="D103">
         <v>123456</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C104">
-        <v>17023181</v>
+        <v>17048826</v>
       </c>
       <c r="D104">
         <v>123456</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C105">
-        <v>17048826</v>
+        <v>17020336</v>
       </c>
       <c r="D105">
         <v>123456</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C106">
-        <v>17020336</v>
+        <v>17018382</v>
       </c>
       <c r="D106">
         <v>123456</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C107">
-        <v>17018382</v>
+        <v>17021251</v>
       </c>
       <c r="D107">
         <v>123456</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C108">
-        <v>17021251</v>
+        <v>17020590</v>
       </c>
       <c r="D108">
         <v>123456</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C109">
-        <v>17020590</v>
+        <v>17052963</v>
       </c>
       <c r="D109">
         <v>123456</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C110">
-        <v>17052963</v>
+        <v>17022819</v>
       </c>
       <c r="D110">
         <v>123456</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C111">
-        <v>17022819</v>
+        <v>17017912</v>
       </c>
       <c r="D111">
         <v>123456</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C112">
-        <v>17017912</v>
+        <v>17055857</v>
       </c>
       <c r="D112">
         <v>123456</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C113">
-        <v>17055857</v>
+        <v>17021561</v>
       </c>
       <c r="D113">
         <v>123456</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C114">
-        <v>17021561</v>
+        <v>17017165</v>
       </c>
       <c r="D114">
         <v>123456</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C115">
-        <v>17017165</v>
+        <v>17020140</v>
       </c>
       <c r="D115">
         <v>123456</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="C116">
-        <v>17020140</v>
+        <v>17023319</v>
       </c>
       <c r="D116">
         <v>123456</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="C117">
-        <v>17023319</v>
+        <v>17040051</v>
       </c>
       <c r="D117">
         <v>123456</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C118">
-        <v>17040051</v>
+        <v>17021596</v>
       </c>
       <c r="D118">
         <v>123456</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C119">
-        <v>17021596</v>
+        <v>17022320</v>
       </c>
       <c r="D119">
         <v>123456</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C120">
-        <v>17022320</v>
+        <v>17036917</v>
       </c>
       <c r="D120">
         <v>123456</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C121">
-        <v>17036917</v>
+        <v>17021146</v>
       </c>
       <c r="D121">
         <v>123456</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C122">
-        <v>17021146</v>
+        <v>17018390</v>
       </c>
       <c r="D122">
         <v>123456</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C123">
-        <v>17018390</v>
+        <v>17020581</v>
       </c>
       <c r="D123">
         <v>123456</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C124">
-        <v>17020581</v>
+        <v>17022312</v>
       </c>
       <c r="D124">
         <v>123456</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C125">
-        <v>17022312</v>
+        <v>17021774</v>
       </c>
       <c r="D125">
         <v>123456</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C126">
-        <v>17021774</v>
+        <v>17022339</v>
       </c>
       <c r="D126">
         <v>123456</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C127">
-        <v>17022339</v>
+        <v>17040035</v>
       </c>
       <c r="D127">
         <v>123456</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C128">
-        <v>17040035</v>
+        <v>17022860</v>
       </c>
       <c r="D128">
         <v>123456</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C129">
-        <v>17022860</v>
+        <v>17020611</v>
       </c>
       <c r="D129">
         <v>123456</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C130">
-        <v>17020611</v>
+        <v>17021588</v>
       </c>
       <c r="D130">
         <v>123456</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C131">
-        <v>17021588</v>
+        <v>17038359</v>
       </c>
       <c r="D131">
         <v>123456</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C132">
-        <v>17038359</v>
+        <v>17018404</v>
       </c>
       <c r="D132">
         <v>123456</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C133">
-        <v>17018404</v>
+        <v>17021731</v>
       </c>
       <c r="D133">
         <v>123456</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C134">
-        <v>17021731</v>
+        <v>17020360</v>
       </c>
       <c r="D134">
         <v>123456</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C135">
-        <v>17020360</v>
+        <v>17040841</v>
       </c>
       <c r="D135">
         <v>123456</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="C136">
-        <v>17040841</v>
+        <v>17020158</v>
       </c>
       <c r="D136">
         <v>123456</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C137">
-        <v>17020158</v>
+        <v>17053315</v>
       </c>
       <c r="D137">
         <v>123456</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C138">
-        <v>17053315</v>
+        <v>17021600</v>
       </c>
       <c r="D138">
         <v>123456</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C139">
-        <v>17021600</v>
+        <v>17017203</v>
       </c>
       <c r="D139">
         <v>123456</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C140">
-        <v>17017203</v>
+        <v>17021707</v>
       </c>
       <c r="D140">
         <v>123456</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C141">
-        <v>17021707</v>
+        <v>17021804</v>
       </c>
       <c r="D141">
         <v>123456</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C142">
-        <v>17021804</v>
+        <v>17106800</v>
       </c>
       <c r="D142">
         <v>123456</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C143">
-        <v>17106800</v>
+        <v>17050278</v>
       </c>
       <c r="D143">
         <v>123456</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C144">
-        <v>17050278</v>
+        <v>17043069</v>
       </c>
       <c r="D144">
         <v>123456</v>
       </c>
     </row>
-    <row r="145" spans="1:4">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C145">
-        <v>17043069</v>
+        <v>17018820</v>
       </c>
       <c r="D145">
         <v>123456</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C146">
-        <v>17018820</v>
+        <v>17043026</v>
       </c>
       <c r="D146">
         <v>123456</v>
       </c>
     </row>
-    <row r="147" spans="1:4">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C147">
-        <v>17043026</v>
+        <v>17039150</v>
       </c>
       <c r="D147">
         <v>123456</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C148">
-        <v>17039150</v>
+        <v>17052823</v>
       </c>
       <c r="D148">
         <v>123456</v>
       </c>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C149">
-        <v>17052823</v>
+        <v>17051746</v>
       </c>
       <c r="D149">
         <v>123456</v>
       </c>
     </row>
-    <row r="150" spans="1:4">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C150">
-        <v>17051746</v>
+        <v>17049253</v>
       </c>
       <c r="D150">
         <v>123456</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C151">
-        <v>17049253</v>
+        <v>17107806</v>
       </c>
       <c r="D151">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4">
-      <c r="A152" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C152">
-        <v>17107806</v>
-      </c>
-      <c r="D152">
         <v>123456</v>
       </c>
     </row>

--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 2 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9055E1B6-1567-491A-BD51-4E00B18A9862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5338758C-FCC7-4670-960A-FD3D2405F7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="172">
   <si>
     <t>CPF</t>
   </si>
@@ -370,15 +370,6 @@
     <t>SENHA</t>
   </si>
   <si>
-    <t>ALEX RILIE MOREIRA RODRIGUES</t>
-  </si>
-  <si>
-    <t>MARCIA PONCE</t>
-  </si>
-  <si>
-    <t>899.900.642-53</t>
-  </si>
-  <si>
     <t>CENTRO DE ENSINO MEDIO ARY RIBEIRO VALADAO FILHO</t>
   </si>
   <si>
@@ -545,9 +536,6 @@
   </si>
   <si>
     <t>626.250.041-34</t>
-  </si>
-  <si>
-    <t>832.866.401-15</t>
   </si>
   <si>
     <t>ESCOLA ESTADUAL PROFESSORA DIVA GOMES DA SILVEIRA COSTA</t>
@@ -588,11 +576,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -908,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
@@ -924,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D1" t="s">
         <v>114</v>
@@ -937,8 +922,8 @@
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="D2">
-        <v>123456</v>
+      <c r="D2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -948,19 +933,19 @@
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="D3">
-        <v>123456</v>
+      <c r="D3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D4">
-        <v>123456</v>
+        <v>170</v>
+      </c>
+      <c r="D4" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -970,8 +955,8 @@
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="D5">
-        <v>123456</v>
+      <c r="D5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -981,8 +966,8 @@
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="D6">
-        <v>123456</v>
+      <c r="D6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -992,8 +977,8 @@
       <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="D7">
-        <v>123456</v>
+      <c r="D7" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1003,8 +988,8 @@
       <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="D8">
-        <v>123456</v>
+      <c r="D8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1014,8 +999,8 @@
       <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="D9">
-        <v>123456</v>
+      <c r="D9" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1025,8 +1010,8 @@
       <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="D10">
-        <v>123456</v>
+      <c r="D10" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1036,8 +1021,8 @@
       <c r="B11" t="s">
         <v>18</v>
       </c>
-      <c r="D11">
-        <v>123456</v>
+      <c r="D11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1047,8 +1032,8 @@
       <c r="B12" t="s">
         <v>20</v>
       </c>
-      <c r="D12">
-        <v>123456</v>
+      <c r="D12" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1058,8 +1043,8 @@
       <c r="B13" t="s">
         <v>22</v>
       </c>
-      <c r="D13">
-        <v>123456</v>
+      <c r="D13" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1069,8 +1054,8 @@
       <c r="B14" t="s">
         <v>24</v>
       </c>
-      <c r="D14">
-        <v>123456</v>
+      <c r="D14" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -1080,8 +1065,8 @@
       <c r="B15" t="s">
         <v>26</v>
       </c>
-      <c r="D15">
-        <v>123456</v>
+      <c r="D15" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -1091,8 +1076,8 @@
       <c r="B16" t="s">
         <v>28</v>
       </c>
-      <c r="D16">
-        <v>123456</v>
+      <c r="D16" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1102,8 +1087,8 @@
       <c r="B17" t="s">
         <v>30</v>
       </c>
-      <c r="D17">
-        <v>123456</v>
+      <c r="D17" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1113,8 +1098,8 @@
       <c r="B18" t="s">
         <v>32</v>
       </c>
-      <c r="D18">
-        <v>123456</v>
+      <c r="D18" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1124,8 +1109,8 @@
       <c r="B19" t="s">
         <v>34</v>
       </c>
-      <c r="D19">
-        <v>123456</v>
+      <c r="D19" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1135,8 +1120,8 @@
       <c r="B20" t="s">
         <v>36</v>
       </c>
-      <c r="D20">
-        <v>123456</v>
+      <c r="D20" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1146,8 +1131,8 @@
       <c r="B21" t="s">
         <v>38</v>
       </c>
-      <c r="D21">
-        <v>123456</v>
+      <c r="D21" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1157,8 +1142,8 @@
       <c r="B22" t="s">
         <v>40</v>
       </c>
-      <c r="D22">
-        <v>123456</v>
+      <c r="D22" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1168,8 +1153,8 @@
       <c r="B23" t="s">
         <v>42</v>
       </c>
-      <c r="D23">
-        <v>123456</v>
+      <c r="D23" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1179,8 +1164,8 @@
       <c r="B24" t="s">
         <v>44</v>
       </c>
-      <c r="D24">
-        <v>123456</v>
+      <c r="D24" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1190,8 +1175,8 @@
       <c r="B25" t="s">
         <v>46</v>
       </c>
-      <c r="D25">
-        <v>123456</v>
+      <c r="D25" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1201,8 +1186,8 @@
       <c r="B26" t="s">
         <v>48</v>
       </c>
-      <c r="D26">
-        <v>123456</v>
+      <c r="D26" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1212,8 +1197,8 @@
       <c r="B27" t="s">
         <v>50</v>
       </c>
-      <c r="D27">
-        <v>123456</v>
+      <c r="D27" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1223,8 +1208,8 @@
       <c r="B28" t="s">
         <v>52</v>
       </c>
-      <c r="D28">
-        <v>123456</v>
+      <c r="D28" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1234,8 +1219,8 @@
       <c r="B29" t="s">
         <v>54</v>
       </c>
-      <c r="D29">
-        <v>123456</v>
+      <c r="D29" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1245,8 +1230,8 @@
       <c r="B30" t="s">
         <v>56</v>
       </c>
-      <c r="D30">
-        <v>123456</v>
+      <c r="D30" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1256,8 +1241,8 @@
       <c r="B31" t="s">
         <v>58</v>
       </c>
-      <c r="D31">
-        <v>123456</v>
+      <c r="D31" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1267,8 +1252,8 @@
       <c r="B32" t="s">
         <v>60</v>
       </c>
-      <c r="D32">
-        <v>123456</v>
+      <c r="D32" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1278,8 +1263,8 @@
       <c r="B33" t="s">
         <v>62</v>
       </c>
-      <c r="D33">
-        <v>123456</v>
+      <c r="D33" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1289,8 +1274,8 @@
       <c r="B34" t="s">
         <v>64</v>
       </c>
-      <c r="D34">
-        <v>123456</v>
+      <c r="D34" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1300,8 +1285,8 @@
       <c r="B35" t="s">
         <v>66</v>
       </c>
-      <c r="D35">
-        <v>123456</v>
+      <c r="D35" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1311,8 +1296,8 @@
       <c r="B36" t="s">
         <v>68</v>
       </c>
-      <c r="D36">
-        <v>123456</v>
+      <c r="D36" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1322,8 +1307,8 @@
       <c r="B37" t="s">
         <v>70</v>
       </c>
-      <c r="D37">
-        <v>123456</v>
+      <c r="D37" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1333,8 +1318,8 @@
       <c r="B38" t="s">
         <v>72</v>
       </c>
-      <c r="D38">
-        <v>123456</v>
+      <c r="D38" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1344,8 +1329,8 @@
       <c r="B39" t="s">
         <v>74</v>
       </c>
-      <c r="D39">
-        <v>123456</v>
+      <c r="D39" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -1355,8 +1340,8 @@
       <c r="B40" t="s">
         <v>76</v>
       </c>
-      <c r="D40">
-        <v>123456</v>
+      <c r="D40" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -1366,8 +1351,8 @@
       <c r="B41" t="s">
         <v>78</v>
       </c>
-      <c r="D41">
-        <v>123456</v>
+      <c r="D41" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1377,8 +1362,8 @@
       <c r="B42" t="s">
         <v>80</v>
       </c>
-      <c r="D42">
-        <v>123456</v>
+      <c r="D42" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1388,8 +1373,8 @@
       <c r="B43" t="s">
         <v>82</v>
       </c>
-      <c r="D43">
-        <v>123456</v>
+      <c r="D43" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -1399,8 +1384,8 @@
       <c r="B44" t="s">
         <v>60</v>
       </c>
-      <c r="D44">
-        <v>123456</v>
+      <c r="D44" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1410,8 +1395,8 @@
       <c r="B45" t="s">
         <v>84</v>
       </c>
-      <c r="D45">
-        <v>123456</v>
+      <c r="D45" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1421,8 +1406,8 @@
       <c r="B46" t="s">
         <v>62</v>
       </c>
-      <c r="D46">
-        <v>123456</v>
+      <c r="D46" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1432,8 +1417,8 @@
       <c r="B47" t="s">
         <v>86</v>
       </c>
-      <c r="D47">
-        <v>123456</v>
+      <c r="D47" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -1443,8 +1428,8 @@
       <c r="B48" t="s">
         <v>88</v>
       </c>
-      <c r="D48">
-        <v>123456</v>
+      <c r="D48" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1454,393 +1439,393 @@
       <c r="B49" t="s">
         <v>38</v>
       </c>
-      <c r="D49">
-        <v>123456</v>
+      <c r="D49" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="B50" t="s">
-        <v>40</v>
-      </c>
-      <c r="D50">
-        <v>123456</v>
+        <v>64</v>
+      </c>
+      <c r="D50" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="B51" t="s">
-        <v>64</v>
-      </c>
-      <c r="D51">
-        <v>123456</v>
+        <v>90</v>
+      </c>
+      <c r="D51" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
-      </c>
-      <c r="D52">
-        <v>123456</v>
+        <v>92</v>
+      </c>
+      <c r="D52" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
-      </c>
-      <c r="D53">
-        <v>123456</v>
+        <v>94</v>
+      </c>
+      <c r="D53" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B54" t="s">
-        <v>94</v>
-      </c>
-      <c r="D54">
-        <v>123456</v>
+        <v>96</v>
+      </c>
+      <c r="D54" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>96</v>
-      </c>
-      <c r="D55">
-        <v>123456</v>
+        <v>66</v>
+      </c>
+      <c r="D55" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
-      </c>
-      <c r="D56">
-        <v>123456</v>
+        <v>50</v>
+      </c>
+      <c r="D56" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>50</v>
-      </c>
-      <c r="D57">
-        <v>123456</v>
+        <v>98</v>
+      </c>
+      <c r="D57" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
-      </c>
-      <c r="D58">
-        <v>123456</v>
+        <v>68</v>
+      </c>
+      <c r="D58" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
-      </c>
-      <c r="D59">
-        <v>123456</v>
+        <v>70</v>
+      </c>
+      <c r="D59" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
-      </c>
-      <c r="D60">
-        <v>123456</v>
+        <v>72</v>
+      </c>
+      <c r="D60" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
-      </c>
-      <c r="D61">
-        <v>123456</v>
+        <v>6</v>
+      </c>
+      <c r="D61" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B62" t="s">
-        <v>6</v>
-      </c>
-      <c r="D62">
-        <v>123456</v>
+        <v>2</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="B63" t="s">
-        <v>2</v>
-      </c>
-      <c r="D63">
-        <v>123456</v>
+        <v>52</v>
+      </c>
+      <c r="D63" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="B64" t="s">
-        <v>52</v>
-      </c>
-      <c r="D64">
-        <v>123456</v>
+        <v>74</v>
+      </c>
+      <c r="D64" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
-      </c>
-      <c r="D65">
-        <v>123456</v>
+        <v>26</v>
+      </c>
+      <c r="D65" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
-      </c>
-      <c r="D66">
-        <v>123456</v>
+        <v>100</v>
+      </c>
+      <c r="D66" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B67" t="s">
-        <v>100</v>
-      </c>
-      <c r="D67">
-        <v>123456</v>
+        <v>102</v>
+      </c>
+      <c r="D67" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>102</v>
-      </c>
-      <c r="D68">
-        <v>123456</v>
+        <v>8</v>
+      </c>
+      <c r="D68" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B69" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69">
-        <v>123456</v>
+        <v>18</v>
+      </c>
+      <c r="D69" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>18</v>
-      </c>
-      <c r="D70">
-        <v>123456</v>
+        <v>10</v>
+      </c>
+      <c r="D70" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B71" t="s">
-        <v>10</v>
-      </c>
-      <c r="D71">
-        <v>123456</v>
+        <v>42</v>
+      </c>
+      <c r="D71" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B72" t="s">
-        <v>42</v>
-      </c>
-      <c r="D72">
-        <v>123456</v>
+        <v>12</v>
+      </c>
+      <c r="D72" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>12</v>
-      </c>
-      <c r="D73">
-        <v>123456</v>
+        <v>78</v>
+      </c>
+      <c r="D73" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="B74" t="s">
-        <v>78</v>
-      </c>
-      <c r="D74">
-        <v>123456</v>
+        <v>20</v>
+      </c>
+      <c r="D74" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B75" t="s">
-        <v>20</v>
-      </c>
-      <c r="D75">
-        <v>123456</v>
+        <v>4</v>
+      </c>
+      <c r="D75" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B76" t="s">
-        <v>4</v>
-      </c>
-      <c r="D76">
-        <v>123456</v>
+        <v>14</v>
+      </c>
+      <c r="D76" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77">
-        <v>123456</v>
+        <v>16</v>
+      </c>
+      <c r="D77" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="D78">
-        <v>123456</v>
+        <v>30</v>
+      </c>
+      <c r="D78" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
-      </c>
-      <c r="D79">
-        <v>123456</v>
+        <v>44</v>
+      </c>
+      <c r="D79" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>44</v>
-      </c>
-      <c r="D80">
-        <v>123456</v>
+        <v>80</v>
+      </c>
+      <c r="D80" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
-      </c>
-      <c r="D81">
-        <v>123456</v>
+        <v>32</v>
+      </c>
+      <c r="D81" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B82" t="s">
-        <v>32</v>
-      </c>
-      <c r="D82">
-        <v>123456</v>
+        <v>54</v>
+      </c>
+      <c r="D82" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B83" t="s">
-        <v>54</v>
-      </c>
-      <c r="D83">
-        <v>123456</v>
+        <v>22</v>
+      </c>
+      <c r="D83" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B84" t="s">
-        <v>22</v>
-      </c>
-      <c r="D84">
-        <v>123456</v>
+        <v>34</v>
+      </c>
+      <c r="D84" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -1850,735 +1835,701 @@
       <c r="B85" t="s">
         <v>34</v>
       </c>
-      <c r="D85">
-        <v>123456</v>
+      <c r="D85" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
-      </c>
-      <c r="D86">
-        <v>123456</v>
+        <v>104</v>
+      </c>
+      <c r="D86" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="B87" t="s">
-        <v>104</v>
-      </c>
-      <c r="D87">
-        <v>123456</v>
+        <v>56</v>
+      </c>
+      <c r="D87" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="B88" t="s">
-        <v>56</v>
-      </c>
-      <c r="D88">
-        <v>123456</v>
+        <v>106</v>
+      </c>
+      <c r="D88" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="B89" t="s">
-        <v>106</v>
-      </c>
-      <c r="D89">
-        <v>123456</v>
+        <v>48</v>
+      </c>
+      <c r="D89" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B90" t="s">
-        <v>48</v>
-      </c>
-      <c r="D90">
-        <v>123456</v>
+        <v>36</v>
+      </c>
+      <c r="D90" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="B91" t="s">
-        <v>36</v>
-      </c>
-      <c r="D91">
-        <v>123456</v>
+        <v>108</v>
+      </c>
+      <c r="D91" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B92" t="s">
-        <v>108</v>
-      </c>
-      <c r="D92">
-        <v>123456</v>
+        <v>110</v>
+      </c>
+      <c r="D92" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B93" t="s">
-        <v>110</v>
-      </c>
-      <c r="D93">
-        <v>123456</v>
+        <v>112</v>
+      </c>
+      <c r="D93" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="B94" t="s">
-        <v>112</v>
-      </c>
-      <c r="D94">
-        <v>123456</v>
+        <v>58</v>
+      </c>
+      <c r="D94" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>59</v>
-      </c>
-      <c r="B95" t="s">
-        <v>58</v>
+        <v>115</v>
+      </c>
+      <c r="C95">
+        <v>17021502</v>
       </c>
       <c r="D95">
-        <v>123456</v>
+        <v>17021502</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>115</v>
-      </c>
-      <c r="B96" s="1" t="s">
+      <c r="A96" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C96">
+        <v>17021685</v>
+      </c>
+      <c r="D96">
+        <v>17021685</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C96" s="1"/>
-      <c r="D96">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>116</v>
-      </c>
-      <c r="B97" t="s">
-        <v>174</v>
+      <c r="C97">
+        <v>17021553</v>
       </c>
       <c r="D97">
-        <v>123456</v>
+        <v>17021553</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+      <c r="A98" s="1" t="s">
         <v>118</v>
       </c>
       <c r="C98">
-        <v>17021502</v>
+        <v>17052351</v>
       </c>
       <c r="D98">
-        <v>123456</v>
+        <v>17052351</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
+      <c r="A99" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C99">
-        <v>17021685</v>
+        <v>17021243</v>
       </c>
       <c r="D99">
-        <v>123456</v>
+        <v>17021243</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C100">
-        <v>17021553</v>
+        <v>17023181</v>
       </c>
       <c r="D100">
-        <v>123456</v>
+        <v>17023181</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="1" t="s">
         <v>121</v>
       </c>
       <c r="C101">
-        <v>17052351</v>
+        <v>17048826</v>
       </c>
       <c r="D101">
-        <v>123456</v>
+        <v>17048826</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="1" t="s">
         <v>122</v>
       </c>
       <c r="C102">
-        <v>17021243</v>
+        <v>17020336</v>
       </c>
       <c r="D102">
-        <v>123456</v>
+        <v>17020336</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
+      <c r="A103" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C103">
-        <v>17023181</v>
+        <v>17018382</v>
       </c>
       <c r="D103">
-        <v>123456</v>
+        <v>17018382</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C104">
-        <v>17048826</v>
+        <v>17021251</v>
       </c>
       <c r="D104">
-        <v>123456</v>
+        <v>17021251</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
+      <c r="A105" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C105">
-        <v>17020336</v>
+        <v>17020590</v>
       </c>
       <c r="D105">
-        <v>123456</v>
+        <v>17020590</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
+      <c r="A106" s="1" t="s">
         <v>126</v>
       </c>
       <c r="C106">
-        <v>17018382</v>
+        <v>17052963</v>
       </c>
       <c r="D106">
-        <v>123456</v>
+        <v>17052963</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
+      <c r="A107" s="1" t="s">
         <v>127</v>
       </c>
       <c r="C107">
-        <v>17021251</v>
+        <v>17022819</v>
       </c>
       <c r="D107">
-        <v>123456</v>
+        <v>17022819</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
+      <c r="A108" s="1" t="s">
         <v>128</v>
       </c>
       <c r="C108">
-        <v>17020590</v>
+        <v>17017912</v>
       </c>
       <c r="D108">
-        <v>123456</v>
+        <v>17017912</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
+      <c r="A109" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C109">
-        <v>17052963</v>
+        <v>17055857</v>
       </c>
       <c r="D109">
-        <v>123456</v>
+        <v>17055857</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
+      <c r="A110" s="1" t="s">
         <v>130</v>
       </c>
       <c r="C110">
-        <v>17022819</v>
+        <v>17021561</v>
       </c>
       <c r="D110">
-        <v>123456</v>
+        <v>17021561</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="1" t="s">
         <v>131</v>
       </c>
       <c r="C111">
-        <v>17017912</v>
+        <v>17017165</v>
       </c>
       <c r="D111">
-        <v>123456</v>
+        <v>17017165</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
+      <c r="A112" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C112">
-        <v>17055857</v>
+        <v>17020140</v>
       </c>
       <c r="D112">
-        <v>123456</v>
+        <v>17020140</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
+      <c r="A113" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C113">
+        <v>17023319</v>
+      </c>
+      <c r="D113">
+        <v>17023319</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C113">
-        <v>17021561</v>
-      </c>
-      <c r="D113">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
+      <c r="C114">
+        <v>17040051</v>
+      </c>
+      <c r="D114">
+        <v>17040051</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C114">
-        <v>17017165</v>
-      </c>
-      <c r="D114">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
+      <c r="C115">
+        <v>17021596</v>
+      </c>
+      <c r="D115">
+        <v>17021596</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C115">
-        <v>17020140</v>
-      </c>
-      <c r="D115">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="C116">
-        <v>17023319</v>
+        <v>17022320</v>
       </c>
       <c r="D116">
-        <v>123456</v>
+        <v>17022320</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C117">
-        <v>17040051</v>
+        <v>17036917</v>
       </c>
       <c r="D117">
-        <v>123456</v>
+        <v>17036917</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
+      <c r="A118" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C118">
-        <v>17021596</v>
+        <v>17021146</v>
       </c>
       <c r="D118">
-        <v>123456</v>
+        <v>17021146</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
+      <c r="A119" s="1" t="s">
         <v>138</v>
       </c>
       <c r="C119">
-        <v>17022320</v>
+        <v>17018390</v>
       </c>
       <c r="D119">
-        <v>123456</v>
+        <v>17018390</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
+      <c r="A120" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C120">
-        <v>17036917</v>
+        <v>17020581</v>
       </c>
       <c r="D120">
-        <v>123456</v>
+        <v>17020581</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
+      <c r="A121" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C121">
-        <v>17021146</v>
+        <v>17022312</v>
       </c>
       <c r="D121">
-        <v>123456</v>
+        <v>17022312</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="1" t="s">
         <v>141</v>
       </c>
       <c r="C122">
-        <v>17018390</v>
+        <v>17021774</v>
       </c>
       <c r="D122">
-        <v>123456</v>
+        <v>17021774</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="1" t="s">
         <v>142</v>
       </c>
       <c r="C123">
-        <v>17020581</v>
+        <v>17022339</v>
       </c>
       <c r="D123">
-        <v>123456</v>
+        <v>17022339</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="2" t="s">
+      <c r="A124" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C124">
-        <v>17022312</v>
+        <v>17040035</v>
       </c>
       <c r="D124">
-        <v>123456</v>
+        <v>17040035</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="2" t="s">
+      <c r="A125" s="1" t="s">
         <v>144</v>
       </c>
       <c r="C125">
-        <v>17021774</v>
+        <v>17022860</v>
       </c>
       <c r="D125">
-        <v>123456</v>
+        <v>17022860</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
+      <c r="A126" s="1" t="s">
         <v>145</v>
       </c>
       <c r="C126">
-        <v>17022339</v>
+        <v>17020611</v>
       </c>
       <c r="D126">
-        <v>123456</v>
+        <v>17020611</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="2" t="s">
+      <c r="A127" s="1" t="s">
         <v>146</v>
       </c>
       <c r="C127">
-        <v>17040035</v>
+        <v>17021588</v>
       </c>
       <c r="D127">
-        <v>123456</v>
+        <v>17021588</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="2" t="s">
+      <c r="A128" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C128">
-        <v>17022860</v>
+        <v>17038359</v>
       </c>
       <c r="D128">
-        <v>123456</v>
+        <v>17038359</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="2" t="s">
+      <c r="A129" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C129">
-        <v>17020611</v>
+        <v>17018404</v>
       </c>
       <c r="D129">
-        <v>123456</v>
+        <v>17018404</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="2" t="s">
+      <c r="A130" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C130">
-        <v>17021588</v>
+        <v>17021731</v>
       </c>
       <c r="D130">
-        <v>123456</v>
+        <v>17021731</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" s="2" t="s">
+      <c r="A131" s="1" t="s">
         <v>150</v>
       </c>
       <c r="C131">
-        <v>17038359</v>
+        <v>17020360</v>
       </c>
       <c r="D131">
-        <v>123456</v>
+        <v>17020360</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C132">
+        <v>17040841</v>
+      </c>
+      <c r="D132">
+        <v>17040841</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C132">
-        <v>17018404</v>
-      </c>
-      <c r="D132">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="2" t="s">
+      <c r="C133">
+        <v>17020158</v>
+      </c>
+      <c r="D133">
+        <v>17020158</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C133">
-        <v>17021731</v>
-      </c>
-      <c r="D133">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="2" t="s">
+      <c r="C134">
+        <v>17053315</v>
+      </c>
+      <c r="D134">
+        <v>17053315</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C134">
-        <v>17020360</v>
-      </c>
-      <c r="D134">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="C135">
-        <v>17040841</v>
+        <v>17021600</v>
       </c>
       <c r="D135">
-        <v>123456</v>
+        <v>17021600</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="2" t="s">
+      <c r="A136" s="1" t="s">
         <v>154</v>
       </c>
       <c r="C136">
-        <v>17020158</v>
+        <v>17017203</v>
       </c>
       <c r="D136">
-        <v>123456</v>
+        <v>17017203</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="2" t="s">
+      <c r="A137" s="1" t="s">
         <v>155</v>
       </c>
       <c r="C137">
-        <v>17053315</v>
+        <v>17021707</v>
       </c>
       <c r="D137">
-        <v>123456</v>
+        <v>17021707</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="2" t="s">
+      <c r="A138" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C138">
-        <v>17021600</v>
+        <v>17021804</v>
       </c>
       <c r="D138">
-        <v>123456</v>
+        <v>17021804</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="2" t="s">
+      <c r="A139" s="1" t="s">
         <v>157</v>
       </c>
       <c r="C139">
-        <v>17017203</v>
+        <v>17106800</v>
       </c>
       <c r="D139">
-        <v>123456</v>
+        <v>17106800</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="2" t="s">
+      <c r="A140" s="1" t="s">
         <v>158</v>
       </c>
       <c r="C140">
-        <v>17021707</v>
+        <v>17050278</v>
       </c>
       <c r="D140">
-        <v>123456</v>
+        <v>17050278</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="2" t="s">
+      <c r="A141" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C141">
-        <v>17021804</v>
+        <v>17043069</v>
       </c>
       <c r="D141">
-        <v>123456</v>
+        <v>17043069</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" s="2" t="s">
+      <c r="A142" s="1" t="s">
         <v>160</v>
       </c>
       <c r="C142">
-        <v>17106800</v>
+        <v>17018820</v>
       </c>
       <c r="D142">
-        <v>123456</v>
+        <v>17018820</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" s="2" t="s">
+      <c r="A143" s="1" t="s">
         <v>161</v>
       </c>
       <c r="C143">
-        <v>17050278</v>
+        <v>17043026</v>
       </c>
       <c r="D143">
-        <v>123456</v>
+        <v>17043026</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="2" t="s">
+      <c r="A144" s="1" t="s">
         <v>162</v>
       </c>
       <c r="C144">
-        <v>17043069</v>
+        <v>17039150</v>
       </c>
       <c r="D144">
-        <v>123456</v>
+        <v>17039150</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" s="2" t="s">
+      <c r="A145" s="1" t="s">
         <v>163</v>
       </c>
       <c r="C145">
-        <v>17018820</v>
+        <v>17052823</v>
       </c>
       <c r="D145">
-        <v>123456</v>
+        <v>17052823</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="2" t="s">
+      <c r="A146" s="1" t="s">
         <v>164</v>
       </c>
       <c r="C146">
-        <v>17043026</v>
+        <v>17051746</v>
       </c>
       <c r="D146">
-        <v>123456</v>
+        <v>17051746</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="2" t="s">
+      <c r="A147" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C147">
-        <v>17039150</v>
+        <v>17049253</v>
       </c>
       <c r="D147">
-        <v>123456</v>
+        <v>17049253</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" s="2" t="s">
+      <c r="A148" s="1" t="s">
         <v>166</v>
       </c>
       <c r="C148">
-        <v>17052823</v>
+        <v>17107806</v>
       </c>
       <c r="D148">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C149">
-        <v>17051746</v>
-      </c>
-      <c r="D149">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C150">
-        <v>17049253</v>
-      </c>
-      <c r="D150">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C151">
         <v>17107806</v>
-      </c>
-      <c r="D151">
-        <v>123456</v>
       </c>
     </row>
   </sheetData>

--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 2 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 2 3 - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5338758C-FCC7-4670-960A-FD3D2405F7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55C632D-767C-4D26-B187-C404A368AD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="174">
   <si>
     <t>CPF</t>
   </si>
@@ -539,13 +539,19 @@
   </si>
   <si>
     <t>ESCOLA ESTADUAL PROFESSORA DIVA GOMES DA SILVEIRA COSTA</t>
+  </si>
+  <si>
+    <t>tolentinoalexandre534@gmail.com</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -554,6 +560,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -573,14 +585,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -893,15 +908,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -914,8 +930,11 @@
       <c r="D1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -926,7 +945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -937,7 +956,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>169</v>
       </c>
@@ -948,7 +967,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -959,7 +978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -970,7 +989,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -981,7 +1000,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -992,7 +1011,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1003,7 +1022,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1014,7 +1033,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1025,7 +1044,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1036,7 +1055,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1047,7 +1066,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1058,7 +1077,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1069,7 +1088,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1080,7 +1099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -1091,7 +1110,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -1102,7 +1121,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -1113,7 +1132,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -1124,7 +1143,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -1135,7 +1154,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -1145,8 +1164,11 @@
       <c r="D22" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F22" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -1157,7 +1179,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -1168,7 +1190,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -1179,7 +1201,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -1190,7 +1212,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>51</v>
       </c>
@@ -1201,7 +1223,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -1212,7 +1234,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -1223,7 +1245,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -1234,7 +1256,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -1245,7 +1267,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -2533,7 +2555,10 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F22" r:id="rId1" xr:uid="{98D756E0-1DB5-45A9-9F62-4D77746A6800}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 - Copia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bf22f0b01d7fe6/Área de Trabalho/Projeto Python/Painel SGE/Painel 1 2 3 - Copia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D48C37-FB49-4A6B-ADB1-FABBFF59DE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A2AAB9F9-1CC5-4B01-8202-B5B8986FFE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3451CA2-1C24-4684-8594-1EC800F0C381}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Modulações Administrativas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modulações Administrativas'!$A$1:$E$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modulações Administrativas'!$A$1:$E$68</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="151">
   <si>
     <t>CPF</t>
   </si>
@@ -473,6 +473,21 @@
   </si>
   <si>
     <t>roberta.silva@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>ALLINE LEMOS LIRA</t>
+  </si>
+  <si>
+    <t>033.867.511-64</t>
+  </si>
+  <si>
+    <t>alline.lira@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>ANDRÉA MARTINS DE PINA</t>
+  </si>
+  <si>
+    <t>andrea.pina@professor.to.gov.br</t>
   </si>
 </sst>
 </file>
@@ -847,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
@@ -945,230 +960,230 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>82</v>
+      </c>
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" t="s">
+        <v>81</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <v>17021502</v>
       </c>
-      <c r="D13">
+      <c r="D14">
         <v>17021502</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14">
-        <v>17021685</v>
-      </c>
-      <c r="D14">
-        <v>17021685</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15">
-        <v>17021553</v>
+        <v>17021685</v>
       </c>
       <c r="D15">
-        <v>17021553</v>
+        <v>17021685</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16">
-        <v>17052351</v>
+        <v>17021553</v>
       </c>
       <c r="D16">
-        <v>17052351</v>
-      </c>
-      <c r="E16" s="2"/>
+        <v>17021553</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17">
-        <v>17021243</v>
+        <v>17052351</v>
       </c>
       <c r="D17">
-        <v>17021243</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>96</v>
-      </c>
+        <v>17052351</v>
+      </c>
+      <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>17023181</v>
+        <v>17021243</v>
       </c>
       <c r="D18">
-        <v>17023181</v>
-      </c>
-      <c r="E18" s="2"/>
+        <v>17021243</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19">
-        <v>17048826</v>
+        <v>17023181</v>
       </c>
       <c r="D19">
-        <v>17048826</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>97</v>
-      </c>
+        <v>17023181</v>
+      </c>
+      <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20">
-        <v>17020336</v>
+        <v>17048826</v>
       </c>
       <c r="D20">
-        <v>17020336</v>
+        <v>17048826</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21">
-        <v>17018382</v>
+        <v>17020336</v>
       </c>
       <c r="D21">
-        <v>17018382</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>101</v>
+        <v>17020336</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22">
-        <v>17021251</v>
+        <v>17018382</v>
       </c>
       <c r="D22">
-        <v>17021251</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>102</v>
+        <v>17018382</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23">
-        <v>17020590</v>
+        <v>17021251</v>
       </c>
       <c r="D23">
-        <v>17020590</v>
+        <v>17021251</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1181,684 +1196,707 @@
       <c r="D24">
         <v>17020590</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>92</v>
+      <c r="E24" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C25">
-        <v>17052963</v>
+        <v>17020590</v>
       </c>
       <c r="D25">
-        <v>17052963</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>103</v>
+        <v>17020590</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C26">
-        <v>17022819</v>
+        <v>17052963</v>
       </c>
       <c r="D26">
-        <v>17022819</v>
+        <v>17052963</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C27">
-        <v>17017912</v>
+        <v>17022819</v>
       </c>
       <c r="D27">
-        <v>17017912</v>
+        <v>17022819</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28">
-        <v>17055857</v>
+        <v>17017912</v>
       </c>
       <c r="D28">
-        <v>17055857</v>
+        <v>17017912</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C29">
-        <v>17021561</v>
+        <v>17055857</v>
       </c>
       <c r="D29">
-        <v>17021561</v>
-      </c>
-      <c r="E29" t="s">
-        <v>107</v>
+        <v>17055857</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C30">
-        <v>17017165</v>
+        <v>17021561</v>
       </c>
       <c r="D30">
-        <v>17017165</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>108</v>
+        <v>17021561</v>
+      </c>
+      <c r="E30" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31">
-        <v>17020140</v>
+        <v>17017165</v>
       </c>
       <c r="D31">
-        <v>17020140</v>
+        <v>17017165</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="C32">
-        <v>17023319</v>
+        <v>17020140</v>
       </c>
       <c r="D32">
-        <v>17023319</v>
+        <v>17020140</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="C33">
-        <v>17040051</v>
+        <v>17023319</v>
       </c>
       <c r="D33">
-        <v>17040051</v>
+        <v>17023319</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C34">
-        <v>17021596</v>
+        <v>17040051</v>
       </c>
       <c r="D34">
-        <v>17021596</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>99</v>
+        <v>17040051</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35">
-        <v>17022320</v>
+        <v>17021596</v>
       </c>
       <c r="D35">
-        <v>17022320</v>
+        <v>17021596</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36">
-        <v>17036917</v>
+        <v>17022320</v>
       </c>
       <c r="D36">
-        <v>17036917</v>
+        <v>17022320</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37">
-        <v>17021146</v>
+        <v>17036917</v>
       </c>
       <c r="D37">
-        <v>17021146</v>
+        <v>17036917</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38">
-        <v>17018390</v>
+        <v>17021146</v>
       </c>
       <c r="D38">
-        <v>17018390</v>
+        <v>17021146</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
-        <v>17020581</v>
+        <v>17018390</v>
       </c>
       <c r="D39">
-        <v>17020581</v>
+        <v>17018390</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
-        <v>17022312</v>
+        <v>17020581</v>
       </c>
       <c r="D40">
-        <v>17022312</v>
+        <v>17020581</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
-        <v>17021774</v>
+        <v>17022312</v>
       </c>
       <c r="D41">
-        <v>17021774</v>
+        <v>17022312</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
-        <v>17022339</v>
+        <v>17021774</v>
       </c>
       <c r="D42">
-        <v>17022339</v>
+        <v>17021774</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
-        <v>17040035</v>
+        <v>17022339</v>
       </c>
       <c r="D43">
-        <v>17040035</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>117</v>
+        <v>17022339</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
-        <v>17022860</v>
+        <v>17040035</v>
       </c>
       <c r="D44">
-        <v>17022860</v>
+        <v>17040035</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
-        <v>17020611</v>
+        <v>17022860</v>
       </c>
       <c r="D45">
-        <v>17020611</v>
+        <v>17022860</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
-        <v>17021588</v>
+        <v>17020611</v>
       </c>
       <c r="D46">
-        <v>17021588</v>
+        <v>17020611</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
-        <v>17038359</v>
+        <v>17021588</v>
       </c>
       <c r="D47">
-        <v>17038359</v>
+        <v>17021588</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
-        <v>17018404</v>
+        <v>17038359</v>
       </c>
       <c r="D48">
-        <v>17018404</v>
+        <v>17038359</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
-        <v>17021731</v>
+        <v>17018404</v>
       </c>
       <c r="D49">
-        <v>17021731</v>
+        <v>17018404</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
-        <v>17020360</v>
+        <v>17021731</v>
       </c>
       <c r="D50">
-        <v>17020360</v>
+        <v>17021731</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C51">
-        <v>17040841</v>
+        <v>17020360</v>
       </c>
       <c r="D51">
-        <v>17040841</v>
+        <v>17020360</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C52">
-        <v>17020158</v>
+        <v>17040841</v>
       </c>
       <c r="D52">
-        <v>17020158</v>
+        <v>17040841</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C53">
-        <v>17053315</v>
+        <v>17020158</v>
       </c>
       <c r="D53">
-        <v>17053315</v>
+        <v>17020158</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C54">
-        <v>17021600</v>
+        <v>17053315</v>
       </c>
       <c r="D54">
-        <v>17021600</v>
+        <v>17053315</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C55">
-        <v>17017203</v>
+        <v>17021600</v>
       </c>
       <c r="D55">
-        <v>17017203</v>
+        <v>17021600</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56">
-        <v>17021707</v>
+        <v>17017203</v>
       </c>
       <c r="D56">
-        <v>17021707</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>91</v>
+        <v>17017203</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C57">
-        <v>17021804</v>
+        <v>17021707</v>
       </c>
       <c r="D57">
-        <v>17021804</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>130</v>
+        <v>17021707</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C58">
-        <v>17106800</v>
+        <v>17021804</v>
       </c>
       <c r="D58">
-        <v>17106800</v>
+        <v>17021804</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C59">
-        <v>17050278</v>
+        <v>17106800</v>
       </c>
       <c r="D59">
-        <v>17050278</v>
+        <v>17106800</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C60">
-        <v>17043069</v>
+        <v>17050278</v>
       </c>
       <c r="D60">
-        <v>17043069</v>
+        <v>17050278</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C61">
-        <v>17018820</v>
+        <v>17043069</v>
       </c>
       <c r="D61">
-        <v>17018820</v>
+        <v>17043069</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C62">
-        <v>17043026</v>
+        <v>17018820</v>
       </c>
       <c r="D62">
-        <v>17043026</v>
+        <v>17018820</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C63">
-        <v>17039150</v>
+        <v>17043026</v>
       </c>
       <c r="D63">
-        <v>17039150</v>
+        <v>17043026</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C64">
-        <v>17052823</v>
+        <v>17039150</v>
       </c>
       <c r="D64">
-        <v>17052823</v>
+        <v>17039150</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65">
-        <v>17051746</v>
+        <v>17052823</v>
       </c>
       <c r="D65">
-        <v>17051746</v>
+        <v>17052823</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C66">
-        <v>17049253</v>
+        <v>17051746</v>
       </c>
       <c r="D66">
-        <v>17049253</v>
+        <v>17051746</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C67">
-        <v>17107806</v>
+        <v>17049253</v>
       </c>
       <c r="D67">
-        <v>17107806</v>
+        <v>17049253</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>142</v>
+        <v>70</v>
+      </c>
+      <c r="C68">
+        <v>17107806</v>
+      </c>
+      <c r="D68">
+        <v>17107806</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>145</v>
       </c>
     </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>149</v>
+      </c>
+      <c r="E71" t="s">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E67" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E68" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="E7" r:id="rId1" xr:uid="{AEE0C3B0-1BF3-48EB-9EA3-5A746517858E}"/>
+    <hyperlink ref="E8" r:id="rId1" xr:uid="{AEE0C3B0-1BF3-48EB-9EA3-5A746517858E}"/>
     <hyperlink ref="E5" r:id="rId2" xr:uid="{FFA4987F-29BF-4F74-8419-9416FABC6C69}"/>
-    <hyperlink ref="E8" r:id="rId3" xr:uid="{9FFBE38D-6766-404F-9093-B70ECCCB57C6}"/>
+    <hyperlink ref="E9" r:id="rId3" xr:uid="{9FFBE38D-6766-404F-9093-B70ECCCB57C6}"/>
     <hyperlink ref="E4" r:id="rId4" xr:uid="{29C73EBE-F4B7-40A5-8305-373C2D7FECF0}"/>
     <hyperlink ref="E3" r:id="rId5" xr:uid="{E2A6B184-7479-4337-95C2-FD418B07CCA7}"/>
-    <hyperlink ref="E11" r:id="rId6" xr:uid="{D01EFA09-D00A-446D-9CBF-BA11FA44A974}"/>
-    <hyperlink ref="E9" r:id="rId7" xr:uid="{B3D75A10-03B2-4F9C-825A-1B5499F96C0C}"/>
-    <hyperlink ref="E10" r:id="rId8" xr:uid="{CEAEB9FE-B633-4EAD-B5BE-4CC1F7E94580}"/>
+    <hyperlink ref="E12" r:id="rId6" xr:uid="{D01EFA09-D00A-446D-9CBF-BA11FA44A974}"/>
+    <hyperlink ref="E10" r:id="rId7" xr:uid="{B3D75A10-03B2-4F9C-825A-1B5499F96C0C}"/>
+    <hyperlink ref="E11" r:id="rId8" xr:uid="{CEAEB9FE-B633-4EAD-B5BE-4CC1F7E94580}"/>
     <hyperlink ref="E2" r:id="rId9" xr:uid="{A47CB573-E728-4F1D-BEE9-F780733C389C}"/>
     <hyperlink ref="E6" r:id="rId10" xr:uid="{AFA83F14-A689-43A6-855D-6CCFA729507F}"/>
-    <hyperlink ref="E12" r:id="rId11" xr:uid="{8EA6AEE0-BF75-4882-8D24-5523F8FC3EF2}"/>
-    <hyperlink ref="E56" r:id="rId12" xr:uid="{AEF2F350-0DDD-4CC3-83D9-532309D4CF1A}"/>
-    <hyperlink ref="E13" r:id="rId13" xr:uid="{87A071E2-C82E-43C2-AFF8-07FB59401B4F}"/>
-    <hyperlink ref="E14" r:id="rId14" xr:uid="{B46330A8-2538-449E-9B35-322B39604CD0}"/>
-    <hyperlink ref="E15" r:id="rId15" xr:uid="{AF04CD14-06B0-477F-854A-FBF0C5FC46C6}"/>
-    <hyperlink ref="E19" r:id="rId16" xr:uid="{456736E6-F5EC-4F85-8E29-563F7384B7FC}"/>
-    <hyperlink ref="E20" r:id="rId17" xr:uid="{E7D78594-C200-4A80-AF9E-B4E73D1A0F07}"/>
-    <hyperlink ref="E21" r:id="rId18" xr:uid="{E91A31D9-E26E-45C1-BED2-8643687FEA6C}"/>
-    <hyperlink ref="E22" r:id="rId19" xr:uid="{13486532-E25E-4444-9FD0-D2523BB3A586}"/>
-    <hyperlink ref="E25" r:id="rId20" xr:uid="{40D2A6AA-BCA3-4EDD-87F7-0E98FD6FA310}"/>
-    <hyperlink ref="E28" r:id="rId21" xr:uid="{979A5FE7-1E83-44AA-8575-B6687D6D0E90}"/>
-    <hyperlink ref="E30" r:id="rId22" xr:uid="{DF38906D-90C8-4794-BCBF-61442F1F47A9}"/>
-    <hyperlink ref="E31" r:id="rId23" xr:uid="{148BE5EB-22A7-4640-A43A-4BBBA78B8020}"/>
-    <hyperlink ref="E32" r:id="rId24" xr:uid="{C67A4692-07D1-4E77-9FDE-08AB7A9F123C}"/>
-    <hyperlink ref="E35" r:id="rId25" xr:uid="{BF64A6D5-AF37-4B6A-8B44-FFA31C249E90}"/>
-    <hyperlink ref="E36" r:id="rId26" xr:uid="{A14B6C9C-465E-48BB-9D5C-4296BB57B151}"/>
-    <hyperlink ref="E37" r:id="rId27" xr:uid="{39510443-E7E4-4CE9-8E4A-D08B3E9C85DD}"/>
-    <hyperlink ref="E38" r:id="rId28" xr:uid="{3B5C8AA2-9997-4D42-9810-45FB1BA410F5}"/>
-    <hyperlink ref="E39" r:id="rId29" xr:uid="{49C1B852-AC98-4776-B42F-9E128C26964E}"/>
-    <hyperlink ref="E40" r:id="rId30" xr:uid="{E0221E73-A5B2-4224-B1C3-069D79890AA1}"/>
-    <hyperlink ref="E41" r:id="rId31" xr:uid="{715A4C08-CD9A-4986-9020-4D01FCC2E174}"/>
-    <hyperlink ref="E43" r:id="rId32" xr:uid="{81F685FB-18AB-40F4-A239-37FEC5A4CC1B}"/>
-    <hyperlink ref="E45" r:id="rId33" xr:uid="{13E1EA31-291A-45AD-A6CE-5082E549CC91}"/>
-    <hyperlink ref="E46" r:id="rId34" xr:uid="{463B1EF7-F3D4-4401-8BA1-AE1106774857}"/>
-    <hyperlink ref="E47" r:id="rId35" xr:uid="{4C64A978-F73B-4864-B8CE-76430ACCE933}"/>
-    <hyperlink ref="E48" r:id="rId36" xr:uid="{77837C35-769C-4BAD-AF95-5DB752134854}"/>
-    <hyperlink ref="E49" r:id="rId37" xr:uid="{6FEB8DAF-42EC-44F5-ACB7-346110109C62}"/>
-    <hyperlink ref="E50" r:id="rId38" xr:uid="{69ACB0D9-BED9-482F-BC8D-D6C2B535CDCA}"/>
-    <hyperlink ref="E51" r:id="rId39" xr:uid="{5F845DF1-FFB0-4A1A-8DD6-6696EBB8C869}"/>
-    <hyperlink ref="E52" r:id="rId40" xr:uid="{B391D205-86ED-47E3-8E9D-036DBEE2748E}"/>
-    <hyperlink ref="E53" r:id="rId41" xr:uid="{E362429D-20F8-4EAA-9815-6EAE94B7B465}"/>
-    <hyperlink ref="E54" r:id="rId42" xr:uid="{3D5EBA38-EE1C-4355-A27B-5536D7ADAC2C}"/>
-    <hyperlink ref="E55" r:id="rId43" xr:uid="{E047D85B-2879-4DD2-9D6D-9007A4573524}"/>
-    <hyperlink ref="E57" r:id="rId44" xr:uid="{51CB0607-1758-44AC-AA97-411B37EA4DF2}"/>
-    <hyperlink ref="E58" r:id="rId45" xr:uid="{3DDA757E-5369-45FE-8361-14E61E25F58B}"/>
-    <hyperlink ref="E59" r:id="rId46" xr:uid="{B6E6FF11-5547-42AA-998A-D83611AB225A}"/>
-    <hyperlink ref="E60" r:id="rId47" xr:uid="{8883127D-7E95-4EC9-B49B-1273AD9B34FE}"/>
-    <hyperlink ref="E61" r:id="rId48" xr:uid="{29D7E259-4058-458C-AE9D-B3FE0FC387DE}"/>
-    <hyperlink ref="E62" r:id="rId49" xr:uid="{226A6085-DC40-48CD-AC61-83C7367D6094}"/>
-    <hyperlink ref="E63" r:id="rId50" display="mailto:escolaindigena_temanare@seduc.to.gov.br" xr:uid="{128FE3F8-2C6C-4DE3-8EE7-DD1A9DA92BC1}"/>
-    <hyperlink ref="E64" r:id="rId51" xr:uid="{4902D51B-5926-44A8-A601-1FE11B4493EF}"/>
-    <hyperlink ref="E65" r:id="rId52" xr:uid="{139FDA3C-B039-42B5-990E-157F8B1ED884}"/>
-    <hyperlink ref="E66" r:id="rId53" xr:uid="{0720110E-7BFA-40FF-A506-42192E1DCB28}"/>
-    <hyperlink ref="E67" r:id="rId54" xr:uid="{D995FEB4-8569-4AA0-A971-E2B2B6A5740E}"/>
-    <hyperlink ref="E23" r:id="rId55" xr:uid="{EFD0FE3D-FFAD-4DF5-A48F-C2E4F3460C4E}"/>
-    <hyperlink ref="E68" r:id="rId56" xr:uid="{4B244151-2680-40D9-98CA-1C6CAEEA6051}"/>
-    <hyperlink ref="E69" r:id="rId57" xr:uid="{8712D512-6735-468E-84CA-60F3EEE40E85}"/>
+    <hyperlink ref="E13" r:id="rId11" xr:uid="{8EA6AEE0-BF75-4882-8D24-5523F8FC3EF2}"/>
+    <hyperlink ref="E57" r:id="rId12" xr:uid="{AEF2F350-0DDD-4CC3-83D9-532309D4CF1A}"/>
+    <hyperlink ref="E14" r:id="rId13" xr:uid="{87A071E2-C82E-43C2-AFF8-07FB59401B4F}"/>
+    <hyperlink ref="E15" r:id="rId14" xr:uid="{B46330A8-2538-449E-9B35-322B39604CD0}"/>
+    <hyperlink ref="E16" r:id="rId15" xr:uid="{AF04CD14-06B0-477F-854A-FBF0C5FC46C6}"/>
+    <hyperlink ref="E20" r:id="rId16" xr:uid="{456736E6-F5EC-4F85-8E29-563F7384B7FC}"/>
+    <hyperlink ref="E21" r:id="rId17" xr:uid="{E7D78594-C200-4A80-AF9E-B4E73D1A0F07}"/>
+    <hyperlink ref="E22" r:id="rId18" xr:uid="{E91A31D9-E26E-45C1-BED2-8643687FEA6C}"/>
+    <hyperlink ref="E23" r:id="rId19" xr:uid="{13486532-E25E-4444-9FD0-D2523BB3A586}"/>
+    <hyperlink ref="E26" r:id="rId20" xr:uid="{40D2A6AA-BCA3-4EDD-87F7-0E98FD6FA310}"/>
+    <hyperlink ref="E29" r:id="rId21" xr:uid="{979A5FE7-1E83-44AA-8575-B6687D6D0E90}"/>
+    <hyperlink ref="E31" r:id="rId22" xr:uid="{DF38906D-90C8-4794-BCBF-61442F1F47A9}"/>
+    <hyperlink ref="E32" r:id="rId23" xr:uid="{148BE5EB-22A7-4640-A43A-4BBBA78B8020}"/>
+    <hyperlink ref="E33" r:id="rId24" xr:uid="{C67A4692-07D1-4E77-9FDE-08AB7A9F123C}"/>
+    <hyperlink ref="E36" r:id="rId25" xr:uid="{BF64A6D5-AF37-4B6A-8B44-FFA31C249E90}"/>
+    <hyperlink ref="E37" r:id="rId26" xr:uid="{A14B6C9C-465E-48BB-9D5C-4296BB57B151}"/>
+    <hyperlink ref="E38" r:id="rId27" xr:uid="{39510443-E7E4-4CE9-8E4A-D08B3E9C85DD}"/>
+    <hyperlink ref="E39" r:id="rId28" xr:uid="{3B5C8AA2-9997-4D42-9810-45FB1BA410F5}"/>
+    <hyperlink ref="E40" r:id="rId29" xr:uid="{49C1B852-AC98-4776-B42F-9E128C26964E}"/>
+    <hyperlink ref="E41" r:id="rId30" xr:uid="{E0221E73-A5B2-4224-B1C3-069D79890AA1}"/>
+    <hyperlink ref="E42" r:id="rId31" xr:uid="{715A4C08-CD9A-4986-9020-4D01FCC2E174}"/>
+    <hyperlink ref="E44" r:id="rId32" xr:uid="{81F685FB-18AB-40F4-A239-37FEC5A4CC1B}"/>
+    <hyperlink ref="E46" r:id="rId33" xr:uid="{13E1EA31-291A-45AD-A6CE-5082E549CC91}"/>
+    <hyperlink ref="E47" r:id="rId34" xr:uid="{463B1EF7-F3D4-4401-8BA1-AE1106774857}"/>
+    <hyperlink ref="E48" r:id="rId35" xr:uid="{4C64A978-F73B-4864-B8CE-76430ACCE933}"/>
+    <hyperlink ref="E49" r:id="rId36" xr:uid="{77837C35-769C-4BAD-AF95-5DB752134854}"/>
+    <hyperlink ref="E50" r:id="rId37" xr:uid="{6FEB8DAF-42EC-44F5-ACB7-346110109C62}"/>
+    <hyperlink ref="E51" r:id="rId38" xr:uid="{69ACB0D9-BED9-482F-BC8D-D6C2B535CDCA}"/>
+    <hyperlink ref="E52" r:id="rId39" xr:uid="{5F845DF1-FFB0-4A1A-8DD6-6696EBB8C869}"/>
+    <hyperlink ref="E53" r:id="rId40" xr:uid="{B391D205-86ED-47E3-8E9D-036DBEE2748E}"/>
+    <hyperlink ref="E54" r:id="rId41" xr:uid="{E362429D-20F8-4EAA-9815-6EAE94B7B465}"/>
+    <hyperlink ref="E55" r:id="rId42" xr:uid="{3D5EBA38-EE1C-4355-A27B-5536D7ADAC2C}"/>
+    <hyperlink ref="E56" r:id="rId43" xr:uid="{E047D85B-2879-4DD2-9D6D-9007A4573524}"/>
+    <hyperlink ref="E58" r:id="rId44" xr:uid="{51CB0607-1758-44AC-AA97-411B37EA4DF2}"/>
+    <hyperlink ref="E59" r:id="rId45" xr:uid="{3DDA757E-5369-45FE-8361-14E61E25F58B}"/>
+    <hyperlink ref="E60" r:id="rId46" xr:uid="{B6E6FF11-5547-42AA-998A-D83611AB225A}"/>
+    <hyperlink ref="E61" r:id="rId47" xr:uid="{8883127D-7E95-4EC9-B49B-1273AD9B34FE}"/>
+    <hyperlink ref="E62" r:id="rId48" xr:uid="{29D7E259-4058-458C-AE9D-B3FE0FC387DE}"/>
+    <hyperlink ref="E63" r:id="rId49" xr:uid="{226A6085-DC40-48CD-AC61-83C7367D6094}"/>
+    <hyperlink ref="E64" r:id="rId50" display="mailto:escolaindigena_temanare@seduc.to.gov.br" xr:uid="{128FE3F8-2C6C-4DE3-8EE7-DD1A9DA92BC1}"/>
+    <hyperlink ref="E65" r:id="rId51" xr:uid="{4902D51B-5926-44A8-A601-1FE11B4493EF}"/>
+    <hyperlink ref="E66" r:id="rId52" xr:uid="{139FDA3C-B039-42B5-990E-157F8B1ED884}"/>
+    <hyperlink ref="E67" r:id="rId53" xr:uid="{0720110E-7BFA-40FF-A506-42192E1DCB28}"/>
+    <hyperlink ref="E68" r:id="rId54" xr:uid="{D995FEB4-8569-4AA0-A971-E2B2B6A5740E}"/>
+    <hyperlink ref="E24" r:id="rId55" xr:uid="{EFD0FE3D-FFAD-4DF5-A48F-C2E4F3460C4E}"/>
+    <hyperlink ref="E69" r:id="rId56" xr:uid="{4B244151-2680-40D9-98CA-1C6CAEEA6051}"/>
+    <hyperlink ref="E70" r:id="rId57" xr:uid="{8712D512-6735-468E-84CA-60F3EEE40E85}"/>
+    <hyperlink ref="E7" r:id="rId58" xr:uid="{837AFF8C-CBEC-495D-8C54-2EF7EE097514}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId58"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId59"/>
 </worksheet>
 </file>
--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bf22f0b01d7fe6/Área de Trabalho/Projeto Python/Painel SGE/Painel 1 2 3 - Copia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bf22f0b01d7fe6/Área de Trabalho/Projeto Python/Painel SGE/Painel 1 - Copia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A2AAB9F9-1CC5-4B01-8202-B5B8986FFE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3451CA2-1C24-4684-8594-1EC800F0C381}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{A2AAB9F9-1CC5-4B01-8202-B5B8986FFE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4282688-C39D-4670-B7DB-FA9767DC674A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="236">
   <si>
     <t>CPF</t>
   </si>
@@ -484,17 +484,272 @@
     <t>alline.lira@professor.to.gov.br</t>
   </si>
   <si>
+    <t>andrea.pina@professor.to.gov.br</t>
+  </si>
+  <si>
     <t>ANDRÉA MARTINS DE PINA</t>
   </si>
   <si>
-    <t>andrea.pina@professor.to.gov.br</t>
+    <t>KEILA DUARTE LIMA ROSA</t>
+  </si>
+  <si>
+    <t>ZILMA SALES DE SOUZA</t>
+  </si>
+  <si>
+    <t>LUSIVONE GONCALVES ABREU PINHEIRO</t>
+  </si>
+  <si>
+    <t>ELIANE ALVES DE AZEVEDO SANTANA</t>
+  </si>
+  <si>
+    <t>DEBORA REGINA DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>LUCIANA PEREIRA GOMES</t>
+  </si>
+  <si>
+    <t>JULIANA FRASCARI PINTO OLIVEIRA</t>
+  </si>
+  <si>
+    <t>MARIA IRANY BARBOSA PINTO</t>
+  </si>
+  <si>
+    <t>REIJANE ALVES DOS SANTOS MACEDO</t>
+  </si>
+  <si>
+    <t>ROSANGELA MENDES MACIEL SANTOS</t>
+  </si>
+  <si>
+    <t>LUDIMILLA RAMOS SILVA BEZERRA</t>
+  </si>
+  <si>
+    <t>SUENNY FERREIRA CRUZ</t>
+  </si>
+  <si>
+    <t>POLLYANA DE GODOY BORGES</t>
+  </si>
+  <si>
+    <t>SYNARA NUNES RIBEIRO</t>
+  </si>
+  <si>
+    <t>ELIUDE FERNANDES DA SILVA MOURA</t>
+  </si>
+  <si>
+    <t>MARIA JOANA MONTEIRO PORTILHO BARROS</t>
+  </si>
+  <si>
+    <t>POLIANA FERREIRA DE MOURA COÊLHO</t>
+  </si>
+  <si>
+    <t>LINA MARIA DA SILVA CONCESSO</t>
+  </si>
+  <si>
+    <t>AYRANA GOMES FERREIRA</t>
+  </si>
+  <si>
+    <t>ROSEANE SOUZA PEREIRA</t>
+  </si>
+  <si>
+    <t>LIDIANE RODRIGUES PEREIRA</t>
+  </si>
+  <si>
+    <t>ALINE REIS DOS SANTOS MARTINS</t>
+  </si>
+  <si>
+    <t>MARLI FERREIRA VIEIRA FONSECA</t>
+  </si>
+  <si>
+    <t>VIVIANO IESORU JAVAÉ KARAJÁ</t>
+  </si>
+  <si>
+    <t>CLAUDILENE SEIJA TORRES JAVAÉ</t>
+  </si>
+  <si>
+    <t>ORLENE DE SOUSA R. JÁCOME</t>
+  </si>
+  <si>
+    <t>VALDIRENE ALVES LIMA</t>
+  </si>
+  <si>
+    <t>MARIA DE FÁTIMA MARQUES DE OLIVEIRA SANTANA</t>
+  </si>
+  <si>
+    <t>626.250.041-34</t>
+  </si>
+  <si>
+    <t>623.532.171-68</t>
+  </si>
+  <si>
+    <t>575.111.281-49</t>
+  </si>
+  <si>
+    <t>758.444.861-53</t>
+  </si>
+  <si>
+    <t>371.383.751-15</t>
+  </si>
+  <si>
+    <t>008.869.971-43</t>
+  </si>
+  <si>
+    <t>038.389.916-80</t>
+  </si>
+  <si>
+    <t>003.073.171-29</t>
+  </si>
+  <si>
+    <t>012.087.871-28</t>
+  </si>
+  <si>
+    <t>827.967.001-78</t>
+  </si>
+  <si>
+    <t>000.010.751-44</t>
+  </si>
+  <si>
+    <t>003.885.911-45</t>
+  </si>
+  <si>
+    <t>014.827.731-47</t>
+  </si>
+  <si>
+    <t>882.447.251-68</t>
+  </si>
+  <si>
+    <t>985.670.631-91</t>
+  </si>
+  <si>
+    <t>800.627.251-49</t>
+  </si>
+  <si>
+    <t>019.762.211-96</t>
+  </si>
+  <si>
+    <t>340.951.601-87</t>
+  </si>
+  <si>
+    <t>076.079.991-16</t>
+  </si>
+  <si>
+    <t>034.963.001-16</t>
+  </si>
+  <si>
+    <t>010.515.591-89</t>
+  </si>
+  <si>
+    <t>066.914.441-08</t>
+  </si>
+  <si>
+    <t>435.003.151-00</t>
+  </si>
+  <si>
+    <t>016.528.091-39</t>
+  </si>
+  <si>
+    <t>071.338.531-67</t>
+  </si>
+  <si>
+    <t>451.680.081-00</t>
+  </si>
+  <si>
+    <t>006.309.481-94</t>
+  </si>
+  <si>
+    <t>315.567.871-20</t>
+  </si>
+  <si>
+    <t>964.858.761-20</t>
+  </si>
+  <si>
+    <t>lusivoneabreu01@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>elianeasantana@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>deboraazevedo@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>lucianapereiragomes@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>julianafrascarioliveira@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>mariairanypinto17@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>reijanealvesmacedo@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>rosangelammaciel@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>Não Possui (E preciso solicitar)</t>
+  </si>
+  <si>
+    <t>suennycruz@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>pollyana.borges@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>synararibeiro@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>eliudesilvamoura@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>mariajoanaportilhobarros@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>poliana.coelho@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>lina.concesso@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>ayrana.ferreira@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>roseanesouza@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>lidiane.pereira@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>marlifonseca@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>vivianokaraja202323@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>claudilene.javae@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>orlene.jacome@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>valdirene.lima@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>maria.fatimasantana@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">andrea.pina@professor.to.gov.br </t>
+  </si>
+  <si>
+    <t>zilmaribeiro@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">keilarosa@seduc.to.gov.br </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -517,6 +772,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -526,7 +787,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -534,12 +795,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -547,6 +823,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -563,6 +842,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -862,13 +1145,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1827,11 +2110,374 @@
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="A71" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E104" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="E71" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -1895,8 +2541,11 @@
     <hyperlink ref="E69" r:id="rId56" xr:uid="{4B244151-2680-40D9-98CA-1C6CAEEA6051}"/>
     <hyperlink ref="E70" r:id="rId57" xr:uid="{8712D512-6735-468E-84CA-60F3EEE40E85}"/>
     <hyperlink ref="E7" r:id="rId58" xr:uid="{837AFF8C-CBEC-495D-8C54-2EF7EE097514}"/>
+    <hyperlink ref="E71" r:id="rId59" xr:uid="{8578D14F-F5C7-4B4F-9324-52C4E9DDA4D9}"/>
+    <hyperlink ref="E72" r:id="rId60" xr:uid="{03D3228E-2A04-4F16-B558-0099E265701C}"/>
+    <hyperlink ref="E90" r:id="rId61" xr:uid="{8426E286-B438-4344-82EE-CEE4BC8593E7}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId59"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId62"/>
 </worksheet>
 </file>